--- a/data/example_filled_template.xlsx
+++ b/data/example_filled_template.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Дані" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,16 +22,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="35">
   <si>
-    <t xml:space="preserve">Регіон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Виріб</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наявна кількість</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Потреба</t>
+    <t xml:space="preserve">region_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required_quantity</t>
   </si>
   <si>
     <t xml:space="preserve">Київ</t>
@@ -55,57 +55,63 @@
     <t xml:space="preserve">захисний одяг</t>
   </si>
   <si>
+    <t xml:space="preserve">Вінницька область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Волинська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дніпропетровська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Донецька область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Житомирська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закарпатська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запорізька область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Івано-Франківська область</t>
+  </si>
+  <si>
     <t xml:space="preserve">Київська область</t>
   </si>
   <si>
+    <t xml:space="preserve">Кіровоградська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Луганська область</t>
+  </si>
+  <si>
     <t xml:space="preserve">Львівська область</t>
   </si>
   <si>
+    <t xml:space="preserve">Миколаївська область</t>
+  </si>
+  <si>
     <t xml:space="preserve">Одеська область</t>
   </si>
   <si>
+    <t xml:space="preserve">Полтавська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рівненська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сумська область</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тернопільська область</t>
+  </si>
+  <si>
     <t xml:space="preserve">Харківська область</t>
   </si>
   <si>
-    <t xml:space="preserve">Дніпропетровська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Полтавська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сумська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вінницька область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Волинська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Закарпатська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Запорізька область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Івано-Франківська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кіровоградська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Луганська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Миколаївська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рівненська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тернопільська область</t>
-  </si>
-  <si>
     <t xml:space="preserve">Херсонська область</t>
   </si>
   <si>
@@ -115,16 +121,10 @@
     <t xml:space="preserve">Черкаська область</t>
   </si>
   <si>
+    <t xml:space="preserve">Чернівецька область</t>
+  </si>
+  <si>
     <t xml:space="preserve">Чернігівська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чернівецька область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Житомирська область</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Донецька область</t>
   </si>
 </sst>
 </file>
@@ -417,11 +417,6 @@
   </sheetPr>
   <dimension ref="A1:D151"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="17.11"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -445,10 +440,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>14</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -459,10 +454,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -473,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>28</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -487,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -501,10 +496,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -515,10 +510,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>49</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -529,10 +524,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>14</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -543,10 +538,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -557,10 +552,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -571,10 +566,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>35</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -585,10 +580,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>42</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -599,10 +594,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -613,10 +608,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>14</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -627,10 +622,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -641,10 +636,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -655,10 +650,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>35</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -669,10 +664,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -683,10 +678,10 @@
         <v>10</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -697,10 +692,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>14</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -711,10 +706,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -725,10 +720,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -739,10 +734,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>35</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -753,10 +748,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -767,10 +762,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -781,10 +776,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>14</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,10 +790,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -809,10 +804,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>28</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,10 +818,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -837,10 +832,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,10 +846,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -865,10 +860,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -879,10 +874,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>21</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -893,10 +888,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="0" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -907,10 +902,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>35</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -921,10 +916,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>42</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -935,10 +930,10 @@
         <v>10</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>49</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -949,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -963,10 +958,10 @@
         <v>6</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>21</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -977,10 +972,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>28</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -991,10 +986,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>35</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1005,10 +1000,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1019,10 +1014,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1033,10 +1028,10 @@
         <v>5</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>14</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1047,10 +1042,10 @@
         <v>6</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1061,10 +1056,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="0" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>28</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1075,10 +1070,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1089,10 +1084,10 @@
         <v>9</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1103,10 +1098,10 @@
         <v>10</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1117,10 +1112,10 @@
         <v>5</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1131,10 +1126,10 @@
         <v>6</v>
       </c>
       <c r="C51" s="0" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>21</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1145,10 +1140,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="0" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>28</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1159,10 +1154,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1173,10 +1168,10 @@
         <v>9</v>
       </c>
       <c r="C54" s="0" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>42</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1187,10 +1182,10 @@
         <v>10</v>
       </c>
       <c r="C55" s="0" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1201,10 +1196,10 @@
         <v>5</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1215,10 +1210,10 @@
         <v>6</v>
       </c>
       <c r="C57" s="0" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1229,10 +1224,10 @@
         <v>7</v>
       </c>
       <c r="C58" s="0" t="n">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1243,10 +1238,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1257,10 +1252,10 @@
         <v>9</v>
       </c>
       <c r="C60" s="0" t="n">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,10 +1266,10 @@
         <v>10</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1285,10 +1280,10 @@
         <v>5</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>14</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1299,10 +1294,10 @@
         <v>6</v>
       </c>
       <c r="C63" s="0" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>21</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1313,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1327,10 +1322,10 @@
         <v>8</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>35</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1341,10 +1336,10 @@
         <v>9</v>
       </c>
       <c r="C66" s="0" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1355,10 +1350,10 @@
         <v>10</v>
       </c>
       <c r="C67" s="0" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1369,10 +1364,10 @@
         <v>5</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1383,10 +1378,10 @@
         <v>6</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1397,10 +1392,10 @@
         <v>7</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1411,10 +1406,10 @@
         <v>8</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,10 +1420,10 @@
         <v>9</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>42</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1439,10 +1434,10 @@
         <v>10</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1453,10 +1448,10 @@
         <v>5</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1467,10 +1462,10 @@
         <v>6</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1481,10 +1476,10 @@
         <v>7</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1495,10 +1490,10 @@
         <v>8</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,10 +1504,10 @@
         <v>9</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1523,10 +1518,10 @@
         <v>10</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1537,10 +1532,10 @@
         <v>5</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>14</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1551,10 +1546,10 @@
         <v>6</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>21</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1565,10 +1560,10 @@
         <v>7</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>28</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,10 +1574,10 @@
         <v>8</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>35</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1593,10 +1588,10 @@
         <v>9</v>
       </c>
       <c r="C84" s="0" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,10 +1602,10 @@
         <v>10</v>
       </c>
       <c r="C85" s="0" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="C86" s="0" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>14</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1635,10 +1630,10 @@
         <v>6</v>
       </c>
       <c r="C87" s="0" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1649,10 +1644,10 @@
         <v>7</v>
       </c>
       <c r="C88" s="0" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>28</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1663,10 +1658,10 @@
         <v>8</v>
       </c>
       <c r="C89" s="0" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>35</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1677,10 +1672,10 @@
         <v>9</v>
       </c>
       <c r="C90" s="0" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1691,10 +1686,10 @@
         <v>10</v>
       </c>
       <c r="C91" s="0" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1705,10 +1700,10 @@
         <v>5</v>
       </c>
       <c r="C92" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>14</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1719,10 +1714,10 @@
         <v>6</v>
       </c>
       <c r="C93" s="0" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>21</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1733,10 +1728,10 @@
         <v>7</v>
       </c>
       <c r="C94" s="0" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1747,10 +1742,10 @@
         <v>8</v>
       </c>
       <c r="C95" s="0" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1761,10 +1756,10 @@
         <v>9</v>
       </c>
       <c r="C96" s="0" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>42</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1775,10 +1770,10 @@
         <v>10</v>
       </c>
       <c r="C97" s="0" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>49</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,10 +1784,10 @@
         <v>5</v>
       </c>
       <c r="C98" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,10 +1798,10 @@
         <v>6</v>
       </c>
       <c r="C99" s="0" t="n">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>21</v>
+        <v>173</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1817,10 +1812,10 @@
         <v>7</v>
       </c>
       <c r="C100" s="0" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1831,10 +1826,10 @@
         <v>8</v>
       </c>
       <c r="C101" s="0" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1845,10 +1840,10 @@
         <v>9</v>
       </c>
       <c r="C102" s="0" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1859,10 +1854,10 @@
         <v>10</v>
       </c>
       <c r="C103" s="0" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>49</v>
+        <v>144</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1873,10 +1868,10 @@
         <v>5</v>
       </c>
       <c r="C104" s="0" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>14</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,10 +1882,10 @@
         <v>6</v>
       </c>
       <c r="C105" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>21</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1901,10 +1896,10 @@
         <v>7</v>
       </c>
       <c r="C106" s="0" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,10 +1910,10 @@
         <v>8</v>
       </c>
       <c r="C107" s="0" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,10 +1924,10 @@
         <v>9</v>
       </c>
       <c r="C108" s="0" t="n">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1943,10 +1938,10 @@
         <v>10</v>
       </c>
       <c r="C109" s="0" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>49</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1957,10 +1952,10 @@
         <v>5</v>
       </c>
       <c r="C110" s="0" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1971,10 +1966,10 @@
         <v>6</v>
       </c>
       <c r="C111" s="0" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1985,10 +1980,10 @@
         <v>7</v>
       </c>
       <c r="C112" s="0" t="n">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>28</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1999,10 +1994,10 @@
         <v>8</v>
       </c>
       <c r="C113" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2013,10 +2008,10 @@
         <v>9</v>
       </c>
       <c r="C114" s="0" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2027,10 +2022,10 @@
         <v>10</v>
       </c>
       <c r="C115" s="0" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2041,10 +2036,10 @@
         <v>5</v>
       </c>
       <c r="C116" s="0" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>14</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2055,10 +2050,10 @@
         <v>6</v>
       </c>
       <c r="C117" s="0" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>21</v>
+        <v>176</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2069,10 +2064,10 @@
         <v>7</v>
       </c>
       <c r="C118" s="0" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2083,10 +2078,10 @@
         <v>8</v>
       </c>
       <c r="C119" s="0" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2097,10 +2092,10 @@
         <v>9</v>
       </c>
       <c r="C120" s="0" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2111,10 +2106,10 @@
         <v>10</v>
       </c>
       <c r="C121" s="0" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2125,10 +2120,10 @@
         <v>5</v>
       </c>
       <c r="C122" s="0" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>14</v>
+        <v>166</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2139,10 +2134,10 @@
         <v>6</v>
       </c>
       <c r="C123" s="0" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>21</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2153,10 +2148,10 @@
         <v>7</v>
       </c>
       <c r="C124" s="0" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,10 +2162,10 @@
         <v>8</v>
       </c>
       <c r="C125" s="0" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2181,10 +2176,10 @@
         <v>9</v>
       </c>
       <c r="C126" s="0" t="n">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>42</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,10 +2190,10 @@
         <v>10</v>
       </c>
       <c r="C127" s="0" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2209,10 +2204,10 @@
         <v>5</v>
       </c>
       <c r="C128" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2223,10 +2218,10 @@
         <v>6</v>
       </c>
       <c r="C129" s="0" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2237,10 +2232,10 @@
         <v>7</v>
       </c>
       <c r="C130" s="0" t="n">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>28</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2251,10 +2246,10 @@
         <v>8</v>
       </c>
       <c r="C131" s="0" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2265,10 +2260,10 @@
         <v>9</v>
       </c>
       <c r="C132" s="0" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2279,10 +2274,10 @@
         <v>10</v>
       </c>
       <c r="C133" s="0" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2293,10 +2288,10 @@
         <v>5</v>
       </c>
       <c r="C134" s="0" t="n">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2307,10 +2302,10 @@
         <v>6</v>
       </c>
       <c r="C135" s="0" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,10 +2316,10 @@
         <v>7</v>
       </c>
       <c r="C136" s="0" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>28</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,10 +2330,10 @@
         <v>8</v>
       </c>
       <c r="C137" s="0" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2349,10 +2344,10 @@
         <v>9</v>
       </c>
       <c r="C138" s="0" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2363,10 +2358,10 @@
         <v>10</v>
       </c>
       <c r="C139" s="0" t="n">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>49</v>
+        <v>200</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2377,10 +2372,10 @@
         <v>5</v>
       </c>
       <c r="C140" s="0" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>14</v>
+        <v>178</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2391,10 +2386,10 @@
         <v>6</v>
       </c>
       <c r="C141" s="0" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2405,10 +2400,10 @@
         <v>7</v>
       </c>
       <c r="C142" s="0" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,10 +2414,10 @@
         <v>8</v>
       </c>
       <c r="C143" s="0" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2433,10 +2428,10 @@
         <v>9</v>
       </c>
       <c r="C144" s="0" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>42</v>
+        <v>169</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2447,10 +2442,10 @@
         <v>10</v>
       </c>
       <c r="C145" s="0" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>49</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2461,10 +2456,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="0" t="n">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>14</v>
+        <v>120</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2475,10 +2470,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="0" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>21</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2489,10 +2484,10 @@
         <v>7</v>
       </c>
       <c r="C148" s="0" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,10 +2498,10 @@
         <v>8</v>
       </c>
       <c r="C149" s="0" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2517,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="C150" s="0" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>42</v>
+        <v>184</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2531,10 +2526,10 @@
         <v>10</v>
       </c>
       <c r="C151" s="0" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
